--- a/Result/profitability/7821.xlsx
+++ b/Result/profitability/7821.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM9"/>
+  <dimension ref="A1:AM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1573,6 +1573,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>7821</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2304</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1828</v>
+      </c>
+      <c r="E10" t="n">
+        <v>476</v>
+      </c>
+      <c r="F10" t="n">
+        <v>20.66</v>
+      </c>
+      <c r="G10" t="n">
+        <v>52</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2.24%</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>11</v>
+      </c>
+      <c r="J10" t="n">
+        <v>63</v>
+      </c>
+      <c r="K10" t="n">
+        <v>55</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.6375000000000001</v>
+      </c>
+      <c r="N10" t="n">
+        <v>23.57375</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.4597701149425287</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-1.149999999999999</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0.05272810637322323</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.1299999999999999</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.3823529411764703</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-4.710000000000001</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-0.1856523452897123</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK10" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
